--- a/result/custom_price.xlsx
+++ b/result/custom_price.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>206.3</v>
+        <v>232.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>825.2</v>
+        <v>931.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>206.3</v>
+        <v>232.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>206.3</v>
+        <v>160</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2138,6 +2138,156 @@
         <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>#% additional Elemental Resistances during Effect</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>#% increased Armour during Effect</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>#% increased Critical Strike Chance during Effect</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>#% increased Evasion Rating during Effect</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>#% increased Movement Speed during Effect</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Diamond Flask</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gain a Flask Charge when you deal a Critical Strike</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>#% reduced Effect of Curses on you during Effect</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
